--- a/pcb/PickAndPlace.xlsx
+++ b/pcb/PickAndPlace.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_08_16" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_08_17" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -772,25 +772,25 @@
     <t>START</t>
   </si>
   <si>
+    <t>45.466mm</t>
+  </si>
+  <si>
+    <t>-111.252mm</t>
+  </si>
+  <si>
+    <t>42.216mm</t>
+  </si>
+  <si>
+    <t>-109.002mm</t>
+  </si>
+  <si>
+    <t>SELECT</t>
+  </si>
+  <si>
     <t>32.512mm</t>
   </si>
   <si>
-    <t>-111.252mm</t>
-  </si>
-  <si>
     <t>29.262mm</t>
-  </si>
-  <si>
-    <t>-109.002mm</t>
-  </si>
-  <si>
-    <t>SELECT</t>
-  </si>
-  <si>
-    <t>45.466mm</t>
-  </si>
-  <si>
-    <t>42.216mm</t>
   </si>
   <si>
     <t>MENU</t>
